--- a/Result/checksun/水泥工業.xlsx
+++ b/Result/checksun/水泥工業.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,22 +1683,22 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1897,11 +1897,15 @@
           <t>14.91</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>15.77</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>15.38</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>15.77</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2654,7 +2658,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2669,22 +2673,22 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2883,11 +2887,15 @@
           <t>15.02</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>15.47</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>15.81</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>15.47</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3640,7 +3648,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3655,22 +3663,22 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3869,11 +3877,15 @@
           <t>15.095</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>15.54</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>15.84</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>15.54</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>15.84</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4626,7 +4638,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4641,22 +4653,22 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4855,11 +4867,15 @@
           <t>15.185</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>15.61</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>15.86</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>15.61</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>15.86</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5612,7 +5628,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5627,22 +5643,22 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5841,11 +5857,15 @@
           <t>15.335</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>15.69</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>15.89</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>15.69</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>15.89</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6598,7 +6618,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6613,22 +6633,22 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6827,11 +6847,15 @@
           <t>15.46</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>15.92</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>15.75</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>15.92</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7584,7 +7608,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7599,22 +7623,22 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7813,11 +7837,15 @@
           <t>15.575</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>15.94</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>15.94</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8570,7 +8598,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8585,22 +8613,22 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8799,11 +8827,15 @@
           <t>15.67</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>15.85</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>15.95</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>15.85</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>15.95</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9556,7 +9588,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9571,22 +9603,22 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9785,11 +9817,15 @@
           <t>15.72</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>15.88</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>15.96</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>15.88</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>15.96</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10542,7 +10578,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10557,7 +10593,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -10771,11 +10807,15 @@
           <t>13.34</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>13.53</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>13.39</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>13.53</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11528,7 +11568,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11543,7 +11583,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -11757,11 +11797,15 @@
           <t>13.355</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>13.54</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>13.54</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12514,7 +12558,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -12529,7 +12573,7 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -12743,11 +12787,15 @@
           <t>13.37</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>13.55</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>13.41</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>13.55</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13500,7 +13548,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -13515,7 +13563,7 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -13729,11 +13777,15 @@
           <t>13.375</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>13.42</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>13.56</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>13.42</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>13.56</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14486,7 +14538,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -14501,7 +14553,7 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -14715,11 +14767,15 @@
           <t>13.38</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>13.57</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>13.43</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>13.57</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15472,7 +15528,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -15487,7 +15543,7 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -15701,11 +15757,15 @@
           <t>13.39</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>13.44</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>13.58</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>13.44</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>13.58</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16458,7 +16518,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -16473,7 +16533,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -16687,11 +16747,15 @@
           <t>13.4</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>13.61</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>13.46</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17444,7 +17508,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17459,7 +17523,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -17673,11 +17737,15 @@
           <t>13.415</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>13.47</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>13.63</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>13.47</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>13.63</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18430,7 +18498,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18445,7 +18513,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -18659,11 +18727,15 @@
           <t>13.43</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>13.48</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>13.66</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>13.48</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>13.66</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19416,7 +19488,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -19431,7 +19503,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -19645,11 +19717,15 @@
           <t>11.1</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>11.62</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>11.24</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>11.62</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20402,7 +20478,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -20417,7 +20493,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -20631,11 +20707,15 @@
           <t>11.09</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>11.64</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>11.26</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>11.64</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21388,7 +21468,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -21403,7 +21483,7 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -21617,11 +21697,15 @@
           <t>11.08</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>11.67</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>11.29</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>11.67</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22374,7 +22458,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -22389,7 +22473,7 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -22603,11 +22687,15 @@
           <t>11.075</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>11.69</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>11.32</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>11.69</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23360,7 +23448,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -23375,7 +23463,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -23589,11 +23677,15 @@
           <t>11.095</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>11.36</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>11.71</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>11.36</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>11.71</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24346,7 +24438,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -24361,7 +24453,7 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -24575,11 +24667,15 @@
           <t>11.125</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>11.74</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>11.39</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>11.74</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25332,7 +25428,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -25347,7 +25443,7 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -25561,11 +25657,15 @@
           <t>11.17</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>11.8</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>11.43</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26318,7 +26418,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -26333,7 +26433,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -26547,11 +26647,15 @@
           <t>11.22</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>11.84</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>11.46</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27304,7 +27408,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27319,7 +27423,7 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
@@ -27533,11 +27637,15 @@
           <t>11.27</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>11.9</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>11.49</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28290,7 +28398,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -28305,22 +28413,22 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28519,11 +28627,15 @@
           <t>26.685</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>26.97</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>26.8</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>26.97</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29276,7 +29388,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -29291,22 +29403,22 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29505,11 +29617,15 @@
           <t>26.695</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>26.8</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>26.99</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30262,7 +30378,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -30277,22 +30393,22 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30491,11 +30607,15 @@
           <t>26.69</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>27.01</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>26.8</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>27.01</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31248,7 +31368,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31263,22 +31383,22 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31477,11 +31597,15 @@
           <t>26.705</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>27.01</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>26.8</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>27.01</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32234,7 +32358,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32249,22 +32373,22 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32463,11 +32587,15 @@
           <t>26.77</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>27</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>26.8</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33220,7 +33348,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -33235,22 +33363,22 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33449,11 +33577,15 @@
           <t>26.83</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>27</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>26.8</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34206,7 +34338,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -34221,22 +34353,22 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34435,11 +34567,15 @@
           <t>26.895</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>27</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>26.81</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>26.81</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35192,7 +35328,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -35207,22 +35343,22 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35421,11 +35557,15 @@
           <t>26.98</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>27</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>26.81</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>26.81</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36178,7 +36318,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -36193,22 +36333,22 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36407,11 +36547,15 @@
           <t>27.07</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>27.02</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>26.82</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>27.02</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>26.82</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37159,12 +37303,12 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -37179,22 +37323,22 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37393,11 +37537,15 @@
           <t>13.145</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>13.16</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>13.14</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>13.16</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -38145,12 +38293,12 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -38165,22 +38313,22 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38379,11 +38527,15 @@
           <t>13.125</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>13.17</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>13.14</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>13.17</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -39131,12 +39283,12 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -39151,22 +39303,22 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39365,11 +39517,15 @@
           <t>13.105</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>13.18</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>13.14</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>13.18</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -40122,7 +40278,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -40137,22 +40293,22 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40351,11 +40507,15 @@
           <t>13.09</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>13.18</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>13.14</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>13.18</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -41108,7 +41268,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -41123,22 +41283,22 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41337,11 +41497,15 @@
           <t>13.095</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>13.2</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>13.15</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -42094,7 +42258,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -42109,22 +42273,22 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42323,11 +42487,15 @@
           <t>13.105</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>13.16</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>13.21</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>13.16</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>13.21</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -43080,7 +43248,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -43095,22 +43263,22 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43309,11 +43477,15 @@
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>13.22</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>13.17</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>13.22</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -44066,7 +44238,7 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -44081,22 +44253,22 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -44295,11 +44467,15 @@
           <t>13.115</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>13.22</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>13.18</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>13.22</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -45047,12 +45223,12 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -45067,22 +45243,22 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -45281,11 +45457,15 @@
           <t>13.12</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>13.23</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>13.18</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>13.23</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
@@ -46028,7 +46208,7 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
@@ -46038,37 +46218,37 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
@@ -46267,11 +46447,15 @@
           <t>35.515</t>
         </is>
       </c>
-      <c r="CQ47" t="n">
-        <v>35.35</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>34.27</v>
+      <c r="CQ47" t="inlineStr">
+        <is>
+          <t>35.35</t>
+        </is>
+      </c>
+      <c r="CR47" t="inlineStr">
+        <is>
+          <t>34.27</t>
+        </is>
       </c>
       <c r="CS47" t="inlineStr">
         <is>
@@ -47009,12 +47193,12 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
@@ -47024,37 +47208,37 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
@@ -47253,11 +47437,15 @@
           <t>35.45</t>
         </is>
       </c>
-      <c r="CQ48" t="n">
-        <v>35.32</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>34.21</v>
+      <c r="CQ48" t="inlineStr">
+        <is>
+          <t>35.32</t>
+        </is>
+      </c>
+      <c r="CR48" t="inlineStr">
+        <is>
+          <t>34.21</t>
+        </is>
       </c>
       <c r="CS48" t="inlineStr">
         <is>
@@ -47995,12 +48183,12 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
@@ -48010,37 +48198,37 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
@@ -48239,11 +48427,15 @@
           <t>35.40499999999999</t>
         </is>
       </c>
-      <c r="CQ49" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="CR49" t="n">
-        <v>34.16</v>
+      <c r="CQ49" t="inlineStr">
+        <is>
+          <t>35.3</t>
+        </is>
+      </c>
+      <c r="CR49" t="inlineStr">
+        <is>
+          <t>34.16</t>
+        </is>
       </c>
       <c r="CS49" t="inlineStr">
         <is>
@@ -48976,17 +49168,17 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
@@ -48996,37 +49188,37 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
@@ -49225,11 +49417,15 @@
           <t>35.325</t>
         </is>
       </c>
-      <c r="CQ50" t="n">
-        <v>35.23</v>
-      </c>
-      <c r="CR50" t="n">
-        <v>34.1</v>
+      <c r="CQ50" t="inlineStr">
+        <is>
+          <t>35.23</t>
+        </is>
+      </c>
+      <c r="CR50" t="inlineStr">
+        <is>
+          <t>34.1</t>
+        </is>
       </c>
       <c r="CS50" t="inlineStr">
         <is>
@@ -49962,17 +50158,17 @@
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
@@ -49982,37 +50178,37 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
@@ -50211,11 +50407,15 @@
           <t>35.325</t>
         </is>
       </c>
-      <c r="CQ51" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="CR51" t="n">
-        <v>34.06</v>
+      <c r="CQ51" t="inlineStr">
+        <is>
+          <t>35.2</t>
+        </is>
+      </c>
+      <c r="CR51" t="inlineStr">
+        <is>
+          <t>34.06</t>
+        </is>
       </c>
       <c r="CS51" t="inlineStr">
         <is>
@@ -50943,62 +51143,62 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV52" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -51197,11 +51397,15 @@
           <t>35.3</t>
         </is>
       </c>
-      <c r="CQ52" t="n">
-        <v>35.16</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>34.01</v>
+      <c r="CQ52" t="inlineStr">
+        <is>
+          <t>35.16</t>
+        </is>
+      </c>
+      <c r="CR52" t="inlineStr">
+        <is>
+          <t>34.01</t>
+        </is>
       </c>
       <c r="CS52" t="inlineStr">
         <is>
@@ -51954,37 +52158,37 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -52183,11 +52387,15 @@
           <t>35.245</t>
         </is>
       </c>
-      <c r="CQ53" t="n">
-        <v>35.13</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>33.98</v>
+      <c r="CQ53" t="inlineStr">
+        <is>
+          <t>35.13</t>
+        </is>
+      </c>
+      <c r="CR53" t="inlineStr">
+        <is>
+          <t>33.98</t>
+        </is>
       </c>
       <c r="CS53" t="inlineStr">
         <is>
@@ -52940,37 +53148,37 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
@@ -53169,11 +53377,15 @@
           <t>35.22</t>
         </is>
       </c>
-      <c r="CQ54" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>33.96</v>
+      <c r="CQ54" t="inlineStr">
+        <is>
+          <t>35.1</t>
+        </is>
+      </c>
+      <c r="CR54" t="inlineStr">
+        <is>
+          <t>33.96</t>
+        </is>
       </c>
       <c r="CS54" t="inlineStr">
         <is>
@@ -53926,7 +54138,7 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
@@ -53941,22 +54153,22 @@
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
@@ -54155,11 +54367,15 @@
           <t>35.2</t>
         </is>
       </c>
-      <c r="CQ55" t="n">
-        <v>35.08</v>
-      </c>
-      <c r="CR55" t="n">
-        <v>33.95</v>
+      <c r="CQ55" t="inlineStr">
+        <is>
+          <t>35.08</t>
+        </is>
+      </c>
+      <c r="CR55" t="inlineStr">
+        <is>
+          <t>33.95</t>
+        </is>
       </c>
       <c r="CS55" t="inlineStr">
         <is>
@@ -54892,34 +55108,34 @@
       </c>
       <c r="AR56" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV56" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AX56" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -54927,22 +55143,22 @@
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
@@ -55141,11 +55357,15 @@
           <t>25.09</t>
         </is>
       </c>
-      <c r="CQ56" t="n">
-        <v>24.72</v>
-      </c>
-      <c r="CR56" t="n">
-        <v>24.49</v>
+      <c r="CQ56" t="inlineStr">
+        <is>
+          <t>24.72</t>
+        </is>
+      </c>
+      <c r="CR56" t="inlineStr">
+        <is>
+          <t>24.49</t>
+        </is>
       </c>
       <c r="CS56" t="inlineStr">
         <is>
@@ -55261,7 +55481,7 @@
       </c>
       <c r="DQ56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR56" t="inlineStr">
@@ -55873,62 +56093,62 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT57" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -56127,11 +56347,15 @@
           <t>24.96</t>
         </is>
       </c>
-      <c r="CQ57" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="CR57" t="n">
-        <v>24.46</v>
+      <c r="CQ57" t="inlineStr">
+        <is>
+          <t>24.69</t>
+        </is>
+      </c>
+      <c r="CR57" t="inlineStr">
+        <is>
+          <t>24.46</t>
+        </is>
       </c>
       <c r="CS57" t="inlineStr">
         <is>
@@ -56247,7 +56471,7 @@
       </c>
       <c r="DQ57" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR57" t="inlineStr">
@@ -56864,17 +57088,17 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
@@ -56884,37 +57108,37 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW58" t="inlineStr">
+      <c r="AX58" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
+      <c r="AY58" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
@@ -57113,11 +57337,15 @@
           <t>24.785</t>
         </is>
       </c>
-      <c r="CQ58" t="n">
-        <v>24.68</v>
-      </c>
-      <c r="CR58" t="n">
-        <v>24.43</v>
+      <c r="CQ58" t="inlineStr">
+        <is>
+          <t>24.68</t>
+        </is>
+      </c>
+      <c r="CR58" t="inlineStr">
+        <is>
+          <t>24.43</t>
+        </is>
       </c>
       <c r="CS58" t="inlineStr">
         <is>
@@ -57233,7 +57461,7 @@
       </c>
       <c r="DQ58" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR58" t="inlineStr">
@@ -57845,22 +58073,22 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
@@ -57870,37 +58098,37 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW59" t="inlineStr">
+      <c r="AX59" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
+      <c r="AY59" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
@@ -58099,11 +58327,15 @@
           <t>24.545</t>
         </is>
       </c>
-      <c r="CQ59" t="n">
-        <v>24.58</v>
-      </c>
-      <c r="CR59" t="n">
-        <v>24.38</v>
+      <c r="CQ59" t="inlineStr">
+        <is>
+          <t>24.58</t>
+        </is>
+      </c>
+      <c r="CR59" t="inlineStr">
+        <is>
+          <t>24.38</t>
+        </is>
       </c>
       <c r="CS59" t="inlineStr">
         <is>
@@ -58219,7 +58451,7 @@
       </c>
       <c r="DQ59" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR59" t="inlineStr">
@@ -58831,22 +59063,22 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
@@ -58856,37 +59088,37 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW60" t="inlineStr">
+      <c r="AX60" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
+      <c r="AY60" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
@@ -59085,11 +59317,15 @@
           <t>24.465</t>
         </is>
       </c>
-      <c r="CQ60" t="n">
-        <v>24.53</v>
-      </c>
-      <c r="CR60" t="n">
-        <v>24.35</v>
+      <c r="CQ60" t="inlineStr">
+        <is>
+          <t>24.53</t>
+        </is>
+      </c>
+      <c r="CR60" t="inlineStr">
+        <is>
+          <t>24.35</t>
+        </is>
       </c>
       <c r="CS60" t="inlineStr">
         <is>
@@ -59205,7 +59441,7 @@
       </c>
       <c r="DQ60" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR60" t="inlineStr">
@@ -59817,22 +60053,22 @@
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU61" t="inlineStr">
@@ -59842,37 +60078,37 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW61" t="inlineStr">
+      <c r="AX61" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
+      <c r="AY61" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
@@ -60071,11 +60307,15 @@
           <t>24.42</t>
         </is>
       </c>
-      <c r="CQ61" t="n">
-        <v>24.48</v>
-      </c>
-      <c r="CR61" t="n">
-        <v>24.32</v>
+      <c r="CQ61" t="inlineStr">
+        <is>
+          <t>24.48</t>
+        </is>
+      </c>
+      <c r="CR61" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
       </c>
       <c r="CS61" t="inlineStr">
         <is>
@@ -60191,7 +60431,7 @@
       </c>
       <c r="DQ61" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR61" t="inlineStr">
@@ -60818,17 +61058,17 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
@@ -60838,27 +61078,27 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
@@ -61057,11 +61297,15 @@
           <t>24.33</t>
         </is>
       </c>
-      <c r="CQ62" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="CR62" t="n">
-        <v>24.28</v>
+      <c r="CQ62" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="CR62" t="inlineStr">
+        <is>
+          <t>24.28</t>
+        </is>
       </c>
       <c r="CS62" t="inlineStr">
         <is>
@@ -61804,7 +62048,7 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
@@ -61814,7 +62058,7 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
@@ -61824,27 +62068,27 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
@@ -62043,11 +62287,15 @@
           <t>24.305</t>
         </is>
       </c>
-      <c r="CQ63" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>24.24</v>
+      <c r="CQ63" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="CR63" t="inlineStr">
+        <is>
+          <t>24.24</t>
+        </is>
       </c>
       <c r="CS63" t="inlineStr">
         <is>
@@ -62790,7 +63038,7 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
@@ -62800,7 +63048,7 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
@@ -62810,27 +63058,27 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
@@ -63029,11 +63277,15 @@
           <t>24.32</t>
         </is>
       </c>
-      <c r="CQ64" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="CR64" t="n">
-        <v>24.22</v>
+      <c r="CQ64" t="inlineStr">
+        <is>
+          <t>24.44</t>
+        </is>
+      </c>
+      <c r="CR64" t="inlineStr">
+        <is>
+          <t>24.22</t>
+        </is>
       </c>
       <c r="CS64" t="inlineStr">
         <is>
